--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-30 09:26</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-30 11:05</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-30 09:26</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-30 11:05</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-30 11:05</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-30 11:12</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-30 11:05</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-30 11:12</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-30 11:12</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-30 11:20</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-30 11:12</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-30 11:20</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-30 11:20</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-30 11:25</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-30 11:20</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-30 11:25</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-30 11:25</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-30 18:01</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-30 11:25</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-30 18:01</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-31 12:04</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-31 12:11</t>
         </is>
       </c>
     </row>
@@ -15760,7 +15760,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-31 12:04</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-31 12:11</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -472,7 +472,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-08-31 19:00</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-01 09:57</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-08-31 19:00</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-01 09:57</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -472,7 +472,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-01 09:57</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-01 17:31</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-01 09:57</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-01 17:31</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -472,7 +472,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-01 17:31</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-02 09:13</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-01 17:31</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-02 09:13</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -472,7 +472,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-02 09:13</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-02 16:54</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-02 09:13</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-02 16:54</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -472,7 +472,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-02 16:54</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-03 09:17</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-02 16:54</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-03 09:17</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -472,7 +472,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-03 09:17</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-03 17:03</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-03 09:17</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-03 17:03</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -472,7 +472,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-03 17:03</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-03 19:12</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-03 17:03</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-03 19:12</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏛️ 設計監造標" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏗️ 工程施工標" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="🏛️ 設計監造標" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="🏗️ 工程施工標" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'🏛️ 設計監造標'!$A$2:$K$276</definedName>
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-03 19:34</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-03 19:43</t>
         </is>
       </c>
     </row>
@@ -15436,7 +15436,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-03 19:34</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-03 19:43</t>
         </is>
       </c>
     </row>

--- a/今日政府電子採購網.xlsx
+++ b/今日政府電子採購網.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-05 09:14</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-05 16:27</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-05 09:14</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-05 16:27</t>
         </is>
       </c>
     </row>
